--- a/docs/sample-output/03-select-service-hotel/estimate.xlsx
+++ b/docs/sample-output/03-select-service-hotel/estimate.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="388">
   <si>
     <t>FINISHES SOLUTIONS</t>
   </si>
   <si>
-    <t>Total Project Cost — Summary   ·   Harbor Point — select-service hotel · Total $30,663,374</t>
+    <t>Total Project Cost — Summary   ·   Harbor Point — select-service hotel · Total $30,605,903</t>
   </si>
   <si>
     <t>COST SUMMARY</t>
@@ -90,7 +90,7 @@
     <t>Research data version</t>
   </si>
   <si>
-    <t>2026.7c60a42879</t>
+    <t>2026.0c737c8255</t>
   </si>
   <si>
     <t>Engine</t>
@@ -99,10 +99,10 @@
     <t>budget-engine-2.0.0</t>
   </si>
   <si>
-    <t>All defaults come from the research data shipped with the app (2026.7c60a42879), escalated to the construction midpoint and adjusted to the project location. Values marked "Derived estimate — verify" have no direct published source.</t>
-  </si>
-  <si>
-    <t>Cost by Component   ·   Harbor Point — select-service hotel · Total $30,663,374</t>
+    <t>All defaults come from the research data shipped with the app (2026.0c737c8255), escalated to the construction midpoint and adjusted to the project location. Values marked "Derived estimate — verify" have no direct published source.</t>
+  </si>
+  <si>
+    <t>Cost by Component   ·   Harbor Point — select-service hotel · Total $30,605,903</t>
   </si>
   <si>
     <t>Component</t>
@@ -147,7 +147,7 @@
     <t>within ($146,345–$334,502)</t>
   </si>
   <si>
-    <t>Cost by Phase   ·   Harbor Point — select-service hotel · Total $30,663,374</t>
+    <t>Cost by Phase   ·   Harbor Point — select-service hotel · Total $30,605,903</t>
   </si>
   <si>
     <t>Phase</t>
@@ -189,7 +189,7 @@
     <t>6.3%</t>
   </si>
   <si>
-    <t>Line-Item Detail   ·   Harbor Point — select-service hotel · Total $30,663,374</t>
+    <t>Line-Item Detail   ·   Harbor Point — select-service hotel · Total $30,605,903</t>
   </si>
   <si>
     <t>Group</t>
@@ -477,7 +477,7 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>Draw Schedules   ·   Harbor Point — select-service hotel · Total $30,663,374</t>
+    <t>Draw Schedules   ·   Harbor Point — select-service hotel · Total $30,605,903</t>
   </si>
   <si>
     <t>PHASE 1 — MONTHLY DRAWS</t>
@@ -549,7 +549,7 @@
     <t>2028-10</t>
   </si>
   <si>
-    <t>Sources &amp; Assumptions   ·   Harbor Point — select-service hotel · Total $30,663,374</t>
+    <t>Sources &amp; Assumptions   ·   Harbor Point — select-service hotel · Total $30,605,903</t>
   </si>
   <si>
     <t>ASSUMPTIONS</t>
@@ -585,7 +585,7 @@
     <t>LTC 60%, rate 7.00%, fee 1.00%</t>
   </si>
   <si>
-    <t>SOURCES (57)</t>
+    <t>SOURCES (58)</t>
   </si>
   <si>
     <t>Ref</t>
@@ -1165,6 +1165,21 @@
   </si>
   <si>
     <t>https://www.rlb.com/wp-content/uploads/sites/4/2026/06/Q2-2026-QCR_7.7.2026.pdf</t>
+  </si>
+  <si>
+    <t>residential/single-family.json#e10</t>
+  </si>
+  <si>
+    <t>Cost of Constructing a Home-2024 (Special Study for Housing Economics)</t>
+  </si>
+  <si>
+    <t>National Association of Home Builders (Eric Lynch)</t>
+  </si>
+  <si>
+    <t>26747 USD/unit (2024)</t>
+  </si>
+  <si>
+    <t>https://nahb.org/-/media/AB4EFC742624475A97A0A62189986FF8.ashx</t>
   </si>
 </sst>
 </file>
@@ -1762,7 +1777,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="5">
-        <v>597530.72</v>
+        <v>547247.74</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1770,7 +1785,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="5">
-        <v>1016871.25</v>
+        <v>1014759.37</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1778,7 +1793,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="5">
-        <v>925921</v>
+        <v>923359.32</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1786,7 +1801,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="5">
-        <v>187365.34</v>
+        <v>184851.19</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1794,7 +1809,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="7">
-        <v>5933197.65</v>
+        <v>5875726.96</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1810,7 +1825,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="7">
-        <v>30663373.6</v>
+        <v>30605902.91</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1849,7 +1864,7 @@
         <v>22</v>
       </c>
       <c r="B21" s="5">
-        <v>12364263.548387097</v>
+        <v>12341089.883064516</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -1977,19 +1992,19 @@
         <v>21431375.95</v>
       </c>
       <c r="E5" s="13">
-        <v>5933197.65</v>
+        <v>5875726.96</v>
       </c>
       <c r="F5" s="13">
         <v>3298800</v>
       </c>
       <c r="G5" s="13">
-        <v>30663373.6</v>
+        <v>30605902.91</v>
       </c>
       <c r="H5" s="13">
-        <v>247285.27096774193</v>
+        <v>246821.79766129033</v>
       </c>
       <c r="I5" s="14">
-        <v>398.8472112382935</v>
+        <v>398.09967364724247</v>
       </c>
       <c r="J5" s="12" t="s">
         <v>42</v>
@@ -2005,13 +2020,13 @@
         <v>21431375.95</v>
       </c>
       <c r="E6" s="16">
-        <v>5933197.65</v>
+        <v>5875726.96</v>
       </c>
       <c r="F6" s="16">
         <v>3298800</v>
       </c>
       <c r="G6" s="16">
-        <v>30663373.6</v>
+        <v>30605902.91</v>
       </c>
       <c r="H6" s="15"/>
       <c r="I6" s="15"/>
@@ -2127,19 +2142,19 @@
         <v>21431375.95</v>
       </c>
       <c r="G5" s="13">
-        <v>5933197.65</v>
+        <v>5875726.96</v>
       </c>
       <c r="H5" s="13">
         <v>3298800</v>
       </c>
       <c r="I5" s="13">
-        <v>30663373.6</v>
+        <v>30605902.91</v>
       </c>
       <c r="J5" s="13">
-        <v>18398024.16</v>
+        <v>18363541.75</v>
       </c>
       <c r="K5" s="13">
-        <v>741940.76</v>
+        <v>739723.9</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -2154,13 +2169,13 @@
         <v>21431375.95</v>
       </c>
       <c r="G6" s="16">
-        <v>5933197.65</v>
+        <v>5875726.96</v>
       </c>
       <c r="H6" s="16">
         <v>3298800</v>
       </c>
       <c r="I6" s="16">
-        <v>30663373.6</v>
+        <v>30605902.91</v>
       </c>
       <c r="J6" s="15"/>
       <c r="K6" s="15"/>
@@ -3381,10 +3396,10 @@
         <v>137</v>
       </c>
       <c r="H43" s="14">
-        <v>4838.18</v>
+        <v>3407.22</v>
       </c>
       <c r="I43" s="13">
-        <v>92989.82</v>
+        <v>65486.77</v>
       </c>
       <c r="J43" s="12" t="s">
         <v>69</v>
@@ -3413,10 +3428,10 @@
         <v>137</v>
       </c>
       <c r="H44" s="14">
-        <v>4592.44</v>
+        <v>3407.22</v>
       </c>
       <c r="I44" s="13">
-        <v>88266.7</v>
+        <v>65486.77</v>
       </c>
       <c r="J44" s="12" t="s">
         <v>69</v>
@@ -3446,7 +3461,7 @@
       </c>
       <c r="H45" s="18"/>
       <c r="I45" s="13">
-        <v>187365.34</v>
+        <v>184851.19</v>
       </c>
       <c r="J45" s="12" t="s">
         <v>69</v>
@@ -3592,7 +3607,7 @@
       </c>
       <c r="H50" s="18"/>
       <c r="I50" s="13">
-        <v>1016871.25</v>
+        <v>1014759.37</v>
       </c>
       <c r="J50" s="12" t="s">
         <v>69</v>
@@ -3620,7 +3635,7 @@
       </c>
       <c r="H51" s="18"/>
       <c r="I51" s="13">
-        <v>741940.76</v>
+        <v>739723.9</v>
       </c>
       <c r="J51" s="12" t="s">
         <v>69</v>
@@ -3648,7 +3663,7 @@
       </c>
       <c r="H52" s="18"/>
       <c r="I52" s="13">
-        <v>183980.24</v>
+        <v>183635.42</v>
       </c>
       <c r="J52" s="12" t="s">
         <v>69</v>
@@ -3668,7 +3683,7 @@
       <c r="G53" s="15"/>
       <c r="H53" s="15"/>
       <c r="I53" s="16">
-        <v>30663373.6</v>
+        <v>30605902.91</v>
       </c>
       <c r="J53" s="15"/>
     </row>
@@ -3767,13 +3782,13 @@
         <v>0</v>
       </c>
       <c r="C6" s="13">
-        <v>2440071.98</v>
+        <v>2389789</v>
       </c>
       <c r="D6" s="13">
         <v>3298800</v>
       </c>
       <c r="E6" s="13">
-        <v>5922852.22</v>
+        <v>5872224.42</v>
       </c>
       <c r="F6" s="13">
         <v>0</v>
@@ -3793,13 +3808,13 @@
         <v>146148.01</v>
       </c>
       <c r="C7" s="13">
-        <v>135116.05</v>
+        <v>134872.57</v>
       </c>
       <c r="D7" s="13">
         <v>0</v>
       </c>
       <c r="E7" s="13">
-        <v>281264.06</v>
+        <v>281020.58</v>
       </c>
       <c r="F7" s="13">
         <v>0</v>
@@ -3819,13 +3834,13 @@
         <v>434457.47</v>
       </c>
       <c r="C8" s="13">
-        <v>135116.04</v>
+        <v>134872.56</v>
       </c>
       <c r="D8" s="13">
         <v>0</v>
       </c>
       <c r="E8" s="13">
-        <v>569573.51</v>
+        <v>569330.03</v>
       </c>
       <c r="F8" s="13">
         <v>0</v>
@@ -3845,13 +3860,13 @@
         <v>710916.15</v>
       </c>
       <c r="C9" s="13">
-        <v>135116.03</v>
+        <v>134872.56</v>
       </c>
       <c r="D9" s="13">
         <v>0</v>
       </c>
       <c r="E9" s="13">
-        <v>846032.18</v>
+        <v>845788.71</v>
       </c>
       <c r="F9" s="13">
         <v>0</v>
@@ -3871,13 +3886,13 @@
         <v>967982.85</v>
       </c>
       <c r="C10" s="13">
-        <v>135116.02</v>
+        <v>134872.55</v>
       </c>
       <c r="D10" s="13">
         <v>0</v>
       </c>
       <c r="E10" s="13">
-        <v>1103098.87</v>
+        <v>1102855.4</v>
       </c>
       <c r="F10" s="13">
         <v>0</v>
@@ -3897,13 +3912,13 @@
         <v>1198645.46</v>
       </c>
       <c r="C11" s="13">
-        <v>135116.02</v>
+        <v>134872.55</v>
       </c>
       <c r="D11" s="13">
         <v>0</v>
       </c>
       <c r="E11" s="13">
-        <v>1333761.48</v>
+        <v>1333518.01</v>
       </c>
       <c r="F11" s="13">
         <v>0</v>
@@ -3923,13 +3938,13 @@
         <v>1396612.2</v>
       </c>
       <c r="C12" s="13">
-        <v>135116.02</v>
+        <v>134872.55</v>
       </c>
       <c r="D12" s="13">
         <v>0</v>
       </c>
       <c r="E12" s="13">
-        <v>1531728.22</v>
+        <v>1531484.75</v>
       </c>
       <c r="F12" s="13">
         <v>0</v>
@@ -3949,22 +3964,22 @@
         <v>1556482.97</v>
       </c>
       <c r="C13" s="13">
-        <v>135116.02</v>
+        <v>134872.55</v>
       </c>
       <c r="D13" s="13">
         <v>0</v>
       </c>
       <c r="E13" s="13">
-        <v>677038.9</v>
+        <v>706139.26</v>
       </c>
       <c r="F13" s="13">
-        <v>1014560.09</v>
+        <v>985216.26</v>
       </c>
       <c r="G13" s="13">
         <v>0</v>
       </c>
       <c r="H13" s="13">
-        <v>1014560.09</v>
+        <v>985216.26</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -3975,7 +3990,7 @@
         <v>1673897.01</v>
       </c>
       <c r="C14" s="13">
-        <v>135116.02</v>
+        <v>134872.55</v>
       </c>
       <c r="D14" s="13">
         <v>0</v>
@@ -3984,13 +3999,13 @@
         <v>0</v>
       </c>
       <c r="F14" s="13">
-        <v>1809013.03</v>
+        <v>1808769.56</v>
       </c>
       <c r="G14" s="13">
-        <v>5918.27</v>
+        <v>5747.09</v>
       </c>
       <c r="H14" s="13">
-        <v>2829491.39</v>
+        <v>2799732.91</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -4001,7 +4016,7 @@
         <v>1745651.4</v>
       </c>
       <c r="C15" s="13">
-        <v>135116.02</v>
+        <v>134872.55</v>
       </c>
       <c r="D15" s="13">
         <v>0</v>
@@ -4010,13 +4025,13 @@
         <v>0</v>
       </c>
       <c r="F15" s="13">
-        <v>1880767.42</v>
+        <v>1880523.95</v>
       </c>
       <c r="G15" s="13">
-        <v>16505.37</v>
+        <v>16331.78</v>
       </c>
       <c r="H15" s="13">
-        <v>4726764.18</v>
+        <v>4696588.64</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -4027,7 +4042,7 @@
         <v>1769788.99</v>
       </c>
       <c r="C16" s="13">
-        <v>135116.02</v>
+        <v>134872.55</v>
       </c>
       <c r="D16" s="13">
         <v>0</v>
@@ -4036,13 +4051,13 @@
         <v>0</v>
       </c>
       <c r="F16" s="13">
-        <v>1904905.01</v>
+        <v>1904661.54</v>
       </c>
       <c r="G16" s="13">
-        <v>27572.79</v>
+        <v>27396.77</v>
       </c>
       <c r="H16" s="13">
-        <v>6659241.98</v>
+        <v>6628646.95</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -4053,7 +4068,7 @@
         <v>1745651.42</v>
       </c>
       <c r="C17" s="13">
-        <v>135116.08</v>
+        <v>134872.6</v>
       </c>
       <c r="D17" s="13">
         <v>0</v>
@@ -4062,13 +4077,13 @@
         <v>0</v>
       </c>
       <c r="F17" s="13">
-        <v>1880767.5</v>
+        <v>1880524.02</v>
       </c>
       <c r="G17" s="13">
-        <v>38845.58</v>
+        <v>38667.11</v>
       </c>
       <c r="H17" s="13">
-        <v>8578855.06</v>
+        <v>8547838.08</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -4079,7 +4094,7 @@
         <v>1673896.96</v>
       </c>
       <c r="C18" s="13">
-        <v>135116.02</v>
+        <v>134872.54</v>
       </c>
       <c r="D18" s="13">
         <v>0</v>
@@ -4088,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="F18" s="13">
-        <v>1809012.98</v>
+        <v>1808769.5</v>
       </c>
       <c r="G18" s="13">
-        <v>50043.32</v>
+        <v>49862.39</v>
       </c>
       <c r="H18" s="13">
-        <v>10437911.36</v>
+        <v>10406469.97</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -4105,7 +4120,7 @@
         <v>1556482.96</v>
       </c>
       <c r="C19" s="13">
-        <v>135116.08</v>
+        <v>134872.6</v>
       </c>
       <c r="D19" s="13">
         <v>0</v>
@@ -4114,13 +4129,13 @@
         <v>0</v>
       </c>
       <c r="F19" s="13">
-        <v>1691599.04</v>
+        <v>1691355.56</v>
       </c>
       <c r="G19" s="13">
-        <v>60887.82</v>
+        <v>60704.41</v>
       </c>
       <c r="H19" s="13">
-        <v>12190398.22</v>
+        <v>12158529.94</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -4131,7 +4146,7 @@
         <v>1396612.2</v>
       </c>
       <c r="C20" s="13">
-        <v>135116.01</v>
+        <v>134872.53</v>
       </c>
       <c r="D20" s="13">
         <v>0</v>
@@ -4140,13 +4155,13 @@
         <v>0</v>
       </c>
       <c r="F20" s="13">
-        <v>1531728.21</v>
+        <v>1531484.73</v>
       </c>
       <c r="G20" s="13">
-        <v>71110.66</v>
+        <v>70924.76</v>
       </c>
       <c r="H20" s="13">
-        <v>13793237.09</v>
+        <v>13760939.43</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -4157,7 +4172,7 @@
         <v>1198645.46</v>
       </c>
       <c r="C21" s="13">
-        <v>135116.08</v>
+        <v>134872.6</v>
       </c>
       <c r="D21" s="13">
         <v>0</v>
@@ -4166,13 +4181,13 @@
         <v>0</v>
       </c>
       <c r="F21" s="13">
-        <v>1333761.54</v>
+        <v>1333518.06</v>
       </c>
       <c r="G21" s="13">
-        <v>80460.55</v>
+        <v>80272.15</v>
       </c>
       <c r="H21" s="13">
-        <v>15207459.18</v>
+        <v>15174729.64</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -4183,7 +4198,7 @@
         <v>967982.79</v>
       </c>
       <c r="C22" s="13">
-        <v>135116.01</v>
+        <v>134872.53</v>
       </c>
       <c r="D22" s="13">
         <v>0</v>
@@ -4192,13 +4207,13 @@
         <v>0</v>
       </c>
       <c r="F22" s="13">
-        <v>1103098.8</v>
+        <v>1102855.32</v>
       </c>
       <c r="G22" s="13">
-        <v>88710.18</v>
+        <v>88519.26</v>
       </c>
       <c r="H22" s="13">
-        <v>16399268.16</v>
+        <v>16366104.22</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -4209,7 +4224,7 @@
         <v>710916.14</v>
       </c>
       <c r="C23" s="13">
-        <v>135116.07</v>
+        <v>134872.59</v>
       </c>
       <c r="D23" s="13">
         <v>0</v>
@@ -4218,13 +4233,13 @@
         <v>0</v>
       </c>
       <c r="F23" s="13">
-        <v>846032.21</v>
+        <v>845788.73</v>
       </c>
       <c r="G23" s="13">
-        <v>95662.4</v>
+        <v>95468.94</v>
       </c>
       <c r="H23" s="13">
-        <v>17340962.77</v>
+        <v>17307361.89</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -4235,7 +4250,7 @@
         <v>434457.5</v>
       </c>
       <c r="C24" s="13">
-        <v>135115.99</v>
+        <v>134872.52</v>
       </c>
       <c r="D24" s="13">
         <v>0</v>
@@ -4244,13 +4259,13 @@
         <v>0</v>
       </c>
       <c r="F24" s="13">
-        <v>569573.49</v>
+        <v>569330.02</v>
       </c>
       <c r="G24" s="13">
-        <v>101155.62</v>
+        <v>100959.61</v>
       </c>
       <c r="H24" s="13">
-        <v>18011691.88</v>
+        <v>17977651.52</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -4261,7 +4276,7 @@
         <v>146148.01</v>
       </c>
       <c r="C25" s="13">
-        <v>135116.07</v>
+        <v>134872.59</v>
       </c>
       <c r="D25" s="13">
         <v>0</v>
@@ -4270,13 +4285,13 @@
         <v>0</v>
       </c>
       <c r="F25" s="13">
-        <v>281264.08</v>
+        <v>281020.6</v>
       </c>
       <c r="G25" s="13">
-        <v>105068.2</v>
+        <v>104869.63</v>
       </c>
       <c r="H25" s="13">
-        <v>18398024.16</v>
+        <v>18363541.75</v>
       </c>
     </row>
   </sheetData>
@@ -4298,7 +4313,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -5543,6 +5558,26 @@
       </c>
       <c r="F68" s="12" t="s">
         <v>382</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="B69" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="E69" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="F69" s="12" t="s">
+        <v>387</v>
       </c>
     </row>
   </sheetData>
